--- a/Security Benchmark - Matrix.xlsx
+++ b/Security Benchmark - Matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idemiapublicsecurityfr-my.sharepoint.com/personal/laurentiu_venin_ps-idemia_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laureven\GiT\Architectures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="737" documentId="8_{6B0482B4-A9E6-440E-B031-C27F46103589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4637EA48-56A9-4943-B449-678EEDC0ACE8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43F0298-B8AF-4785-A2AF-2CC44566F9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. Network Security" sheetId="2" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="12. Artificial Intelligence Sec" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc238419066" localSheetId="0">'01. Network Security'!$B$10</definedName>
-    <definedName name="_Toc238419072" localSheetId="0">'01. Network Security'!$B$33</definedName>
+    <definedName name="_Toc238419066" localSheetId="0">'01. Network Security'!$B$9</definedName>
+    <definedName name="_Toc238419072" localSheetId="0">'01. Network Security'!$B$32</definedName>
     <definedName name="_Toc238419084" localSheetId="1">'02. Identity Management'!$B$31</definedName>
     <definedName name="_Toc238564055" localSheetId="2">'03. Privileged Access'!$A$2</definedName>
     <definedName name="_Toc238564066" localSheetId="3">'10. DevOps Security'!#REF!</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="565">
   <si>
     <t>Capitol</t>
   </si>
@@ -1666,12 +1666,2035 @@
   <si>
     <t>Schedule regular red teaming exercises (monthly or quarterly) accounting for evolving threats and model updates, incorporate threat intelligence from MITRE ATLAS or industry reports to update test scenarios, and use automated tools to enable ongoing testing reducing manual effort while maintaining coverage.</t>
   </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/role-based-access-control/best-practices</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Configuration Settings</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Managed Identity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> allows an Azure workload (VM, App Service, Function, etc.) to authenticate to other Azure services using an identity in Microsoft Entra ID, without storing or managing passwords, client secrets, or keys.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Workload Identity Federatio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">n applies the same secretless principle to external workloads, such as GitHub Actions, Kubernetes, or other platforms, by establishing a trust relationship between the external identity and Microsoft Entra ID.
+After authentication, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Azure RBAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> determines what the workload is allowed to do. Therefore, each workload should have its own identity and only the permissions it strictly requires (least privilege), reducing the impact if that workload is compromised.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Key Vault</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> should not be the first solution for eliminating secrets. First, try to eliminate the secret by using Managed Identity/Federation. If a service still requires a secret, store it in Key Vault and access Key Vault using a Managed Identity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> allows users to authenticate once through Microsoft Entra ID and access multiple applications without repeated authentication. Entra ID therefore becomes the organization’s central identity provider for applications.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Conditional Access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> adds security controls on top of authentication by evaluating the access context — user, application, device, location, and risk — and deciding whether access is allowed, MFA is required, or access must be blocked.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSO answers “Who are you?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>”, while Conditional Access answers “Under what conditions can you access?”. Authorization, through RBAC/Application Roles, then determines “What are you allowed to do?”.
+From a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Zero Trust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> perspective, authentication alone is not enough; access must be explicitly verified and evaluated based on context and risk.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Enable Managed Identity on the VM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+VM → Identity → System assigned → On.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Go to the Storage Account</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Storage Account → Access Control (IAM) → Add role assignment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Select the required RBAC role</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+De exemplu:
+Storage Blob Data Reader – read only
+Storage Blob Data Contributor – read/write
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Assign the role to the VM's Managed Identity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Select Managed Identity → Virtual Machine → select the VM.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Configure the application on the VM to use Managed Identity
+Application obtains an Entra ID access token through the Managed Identity and uses it to access Storage.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Remove stored credentials
+Eliminate Storage Access Keys, connection strings, passwords, and client secrets from the application configuration.
+Verify access
+Test that the application can access Storage with the assigned permissions and cannot perform actions outside its RBAC role.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Microsoft Entra Connect Sync</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> synchronizes identities and selected attributes from on-premises Active Directory Domain Services (AD DS) to Microsoft Entra ID, enabling users to use their organizational identity to access cloud resources and applications.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>AD DS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is the source of identity, while </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Microsoft Entra ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> provides the cloud identity platform. Entra Connect Sync keeps the identities aligned between the two environments.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Synchronization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is not authentication. Entra Connect Sync synchronizes identities, while the authentication method can be Password Hash Synchronization (PHS), Pass-through Authentication (PTA), or federation.
+Once identities are synchronized to Entra ID, you can apply </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>modern cloud security controls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Conditional Access, MFA, Identity Protection, RBAC, and PIM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Application → SSO + Conditional A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ccess
+Register/configure the application in Microsoft Entra ID
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Create or configure the application identity and define the required settings such as Redirect URI.
+Enable Microsoft Entra ID authentication for the application
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">For example, configure App Service → Authentication → Microsoft Entra ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configure user/group access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+In Enterprise Applications → Users and Groups, assign only the users or groups that should access the application.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Create a Conditional Access policy - EntraID Protection - Conditional Access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Define:
+Users/Groups – who is affected
+Target Resource – which application
+Conditions – device, location, risk, etc.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Grant Controls – MFA, compliant device, authentication strength, or Block access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+Start with Report-only mode
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test the policy and review the impact in the Sign-in Logs / Conditional Access reports.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Enable the Conditional Access policy
+After validation, change the policy from Report-only to On.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test the complete access flow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Verify that:
+authorized users can use SSO;
+unauthorized users are blocked;
+MFA is required when appropriate;
+non-compliant or risky devices/sign-ins are handled according to policy.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prepare the on-premises Active Directory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Ensure the AD DS environment is healthy and users/groups have the correct UPNs and attributes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Prepare Microsoft Entra ID
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Verify the organization’s domain (for example, company.com) is configured and verified in Microsoft Entra ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Install Microsoft Entra Connect Sync
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Install Connect Sync on a dedicated Windows Server in the on-premises environment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Connect AD DS to Microsoft Entra ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+During the setup, provide the required AD DS and Microsoft Entra ID administrator credentials.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configure synchronization scope</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Select which domains, OUs, users, and groups should be synchronized. Avoid synchronizing unnecessary objects.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Select the authentication method</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+For example, configure Password Hash Synchronization (PHS) for cloud authentication.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Run the initial synchronization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Synchronize the selected 500 employees from AD DS to Microsoft Entra ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verify synchronization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Confirm that users and groups appear correctly in Microsoft Entra ID and monitor synchronization health.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Apply cloud security controls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Configure MFA, Conditional Access, Identity Protection, PIM, and RBAC as required.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test the complete hybrid identity flow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Test a user signing in to a cloud application and verify that the identity, authentication, and Conditional Access policies work as expected</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Identity Secure Score</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> helps assess the organization’s identity security posture by identifying configuration gaps and security improvement opportunities.
+Focus on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>key areas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> such as privileged role assignments, MFA enforcement, legacy authentication, and application consent policies.
+The goal is not simply to achieve a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>high score</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, but to identify the underlying risks and remediate them using controls such as Conditional Access, PIM, Entra ID Protection, and consent policies.
+Treat it as a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>continuous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> improvement cycle: Assess → Identify Gaps → Prioritize → Remediate → Reassess.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enforce </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>least privilege</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by assigning administrators only the specific Entra ID roles they need instead of broadly assigning Global Administrator.
+Keep a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>small number of Global Administrators</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (typically 2–4) to provide redundancy and recovery while minimizing the attack surface and blast radius.
+Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Microsoft Entra PIM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to make privileged roles eligible rather than permanently active, requiring activation, MFA, justification/approval, and time-limited access when elevated privileges are needed.
+Regularly</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> review administrative access using PIM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Access Reviews, audit logs, and sign-in logs to identify and remove unnecessary privileges.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Identity → Privileged Identity Management → Microsoft Entra ID → Roles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Aici gestionezi rolurile privilegiate.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Creează un assignment PIM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+PIM → Microsoft Entra roles → Roles → [rol] → Add assignments
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurează cerințele de activare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+PIM → Microsoft Entra roles → Settings → [rol] (Require MFA; Require justification; Require approval; Activation maximum duration)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifică activitatea PIM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Identity → Privileged Identity Management → Microsoft Entra roles → Resource audit
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Revizuiește periodic accesul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Identity → Governance → Privileged Identity Management → Microsoft Entra roles → Access reviews</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi User Risk Policy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Microsoft Entra admin center → Protection → Conditional Access → Policies → New policy
+Selectezi: Users &gt; Target Resources &gt; La conditions &gt; User Risk &gt; High (sau ce altceva vrei in politica) &gt; La grant alegi Reuire risk remediation (sau allow sau alceva ce vrei in politica
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Configurezi Sign-in Risk Policy
+Conditional Access → Policies → New policy &gt; Conditions → Sign-in risk Medium and High &gt; la Grant Require multifactor authentication sau block
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blochezi Legacy Authentication
+Conditional Access → Policies → New policy &gt; Configurezi: Users: All users; Target resources: All resources &gt; La Conditionsm Client apps &gt; Exchange ActiveSync clients si /sau Other clients &gt; La Grant Block</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Microsoft</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Entra ID Protection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> detects User Risk (potentially compromised identity) and Sign-in Risk (suspicious authentication attempt).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Conditional Access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> uses these risk signals to enforce access decisions, such as Allow, Require MFA, Require remediation/password change, or Block.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Legacy authenticatio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">n protocols should be blocked because they do not support modern authentication controls such as MFA and Conditional Access effectively, creating a potential path for attackers using stolen credentials.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Use Report-only → Test → Review Sign-in Logs → Adjust → Enable when deploying Conditional Access policies.</t>
+    </r>
+  </si>
+  <si>
+    <t>Microsoft Entra admin center și navighezi către  Identity  Secure Score / recommendations, în funcție de interfața disponibilă.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Configurezi Authentication Methods
+Microsoft Entra admin center →  Authentication methods → Policies &gt; activezi FIDO2 security key: Microsoft Authenticator: metodele necesare pentru Windows Hello for Business
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Înregistrezi utilizatorii
+Creezi Conditional Access pentru MFA
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Microsoft Entra admin center → Protection → Conditional Access → Policies → New policy
+Integrezi cu PIM
+Microsoft Entra ID → Privileged Identity Management → Microsoft Entra roles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Require MFA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for all users to reduce the risk of compromised credentials, while supporting passwordless authentication such as FIDO2 and Windows Hello for Business to reduce dependency on passwords and improve phishing resistance.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Privileged administrators require stronger protection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> because compromising an administrative account can lead to significant or tenant-wide impact. Use Conditional Access to enforce MFA or phishing-resistant authentication for privileged roles.
+Combine</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> PIM with MFA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> so administrators receive privileged access just in time, only when needed, and for a limited period.</t>
+    </r>
+  </si>
+  <si>
+    <t>Microsoft Entra admin center → Identity Protection</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cloud:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Microsoft Entra ID
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On-premises:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Active Directory Domain Services (AD DS)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Create App Registration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Microsoft Entra admin center → Identity → Applications → App registrations → New registration
+Definești: Name; Supported account types; Redirect URI, dacă aplicația are nevoie.
+După creare primești: Application (client) ID și ai: Directory (tenant) ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Creezi/folosești Service Principal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+App Registration are asociată o identitate Service Principal în tenant.
+Poți verifica în: Microsoft Entra ID → Enterprise applications unde vei găsi service principal-ul aplicației.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi credential-ul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Dacă aplicația nu suportă Managed Identity și nici federation, poate folosi: Certificates &amp; secrets
+De preferat: Certificate &gt; Client Secret dacă aplicația suportă certificate.
+Dacă folosești client secret: App registrations → Your App → Certificates &amp; secrets → New client secret
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Assign RBAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Mergi la Storage Account: Storage Account → Access control (IAM) → Add role assignment Alegi rolul minim necesar.
+Exemplu: Storage Blob Data Reader
+Apoi: Assign access to → User, group, or service principal Selectezi Service Principal-ul aplicației.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Managed Identity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> whenever possible because it provides a secretless identity for Azure workloads. When a service does not support Managed Identity, use a Microsoft Entra App Registration and its </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Service Principal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">to represent the application or workload.
+The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Principal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> provides the workload identity and authentication, while Azure RBAC provides authorization, defining exactly what the application can access and what actions it can perform.
+Grant the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Service Principa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>l only the minimum required permissions and, if credentials such as certificates or client secrets are required, protect, rotate, and monitor them carefully.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>App Service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+În:  Azure Portal → App Service → Settings → Configuration → General settings
+Configurezi:
+HTTPS Only = On
+Minimum TLS version → o versiune modernă acceptată de aplicație.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Storage Account</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+În: Storage Account → Configuration verifici setările de transport securizat și te asiguri că: Secure transfer required = Enabled
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>API Management</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+În: API Management → Custom domains / Certificates / Security configurezi certificatele și politicile TLS necesare.</t>
+    </r>
+  </si>
+  <si>
+    <t>Configute TLS encryption</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Microsoft Entra admin center → ID Governance → Entitlement management
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Creezi un Catalog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Mergi la:Entitlement management → Catalogs → New catalog
+Exemplu:
+Catalog:Finance Applications; Adaugi resurse
+În catalog adaugi, de exemplu:
+Finance Applications
+│
+├── Finance-Users Group
+├── SAP Finance
+└── Finance SharePoint Site
+Creezi Access Package</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Entitlement management → Access packages → New access package
+Exemplu:
+Access Package: Finance Application Access; 
+Apoi selectezi resursele: Finance-Users Group; SAP Finance; Finance SharePoint
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi Access Policy</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+De exemplu: All employees
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Approval</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Poți configura:
+Single-stage </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>User ↓ Manager approval ↓Access</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Dual-stage </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>User ↓Manager ↓Resource Owner ↓Access</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Multi-stage </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">User ↓Manager ↓Security Team ↓Resource Owner ↓Access
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi expiration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Poți spune că accesul este: 30 days  sau: 90 days sau o perioadă definită în funcție de policy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Exemplu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>: User requests Finance Access ↓ Approved ↓ Access granted ↓ Valid for 30 days ↓ Expiration ↓ Access automatically removed</t>
+    </r>
+  </si>
+  <si>
+    <t>Microsoft Entra Entitlement Management provides a governed way for users to request access to organizational resources through the My Access portal. Access is delivered through Access Packages, which can include groups, applications, SharePoint sites, and other resources, with single-, dual-, or multi-stage approval workflows based on resource sensitivity.
+Access should be time-bound, with defined expiration and automatic revocation to prevent users from retaining unnecessary access. Notifications and audit logs provide visibility into requests, approvals, denials, and upcoming expirations.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enroll PAW în Intune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Microsoft Intune admin center → Devices - înregistrezi dispozitivul și îl faci managed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creezi Device Configuration Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Devices → Windows → Configuration → Create
+Alegi: Platform: Windows 10 and later și creezi un profil de tip Settings catalog.
+Restricționezi Local Administrator</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Configurezi Screen Lock = 5 minute
+În Settings Catalog cauți setările de: Device Lock și configurezi: Maximum minutes of inactivity until screen locks = 5
+Blochezi removable storage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+În Intune configurezi politicile pentru: Removable Storage / Removable Storage Access
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Restricționezi Microsoft Store
+Configurezi Company Portal
+Intune → Apps → All Apps adaugi aplicațiile aprobate.
+Le atribui grupului: PAW-Users</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pregătești PAW-urile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+În Microsoft Intune: Devices → Windows → Enrollment înrolezi dispozitivele.
+PAW-urile trebuie să fie: Entra joined; Intune managed; compliant. Creezi un grup dedicat
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi Compliance Policy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Intune → Devices → Compliance policies creezi o policy pentru PAW
+De exemplu verifici: BitLocker; Secure Boot; antivirus; firewall; minimum OS version;  Defender status; device integrity.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi phishing-resistant MFA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Microsoft Entra admin center → Protection → Authentication methods activezi metoda necesară.
+Pentru FIDO2: Authentication methods      ↓Passkey / FIDO2      ↓Enable for privileged administrators
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Creezi Conditional Access pentru administratori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Microsoft Entra admin center → Protection → Conditional Access → Policies → New policy
+Exemplu: Name: CA - Privileged Access from PAW
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Selectezi aplicațiile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Target resources / Cloud apps selectezi aplicațiile relevante
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi Device Filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Conditions → Filter for devices configurezi regula pentru PAW-uri
+Conceptual: Device AND Is Entra Joined AND Is Intune Compliant AND Belongs to PAW scope
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi Authentication Strength</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+În Conditional Access: Grant → Require authentication strength
+Blochezi BYOD
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi PIM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Mergi la: Microsoft Entra admin center → ID Governance → Privileged Identity Management
+Apoi: Microsoft Entra roles sau: Azure resources în funcție de rol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Configurezi Activation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Pentru rol configurezi:
+MFA                → Required
+Justification      → Required
+Approval           → Required
+Maximum duration   → 1 hour</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1698,8 +3721,23 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1712,8 +3750,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1749,28 +3793,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1793,8 +3823,41 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1802,21 +3865,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1824,11 +3874,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2109,7 +4154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E27678-48D3-4BC1-B7CE-C1E6C36FC0AB}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="1" bestFit="1" customWidth="1"/>
@@ -2121,19 +4166,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2147,723 +4192,708 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="12" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A3" s="27"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>41</v>
+      <c r="A4" s="27"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>42</v>
+      <c r="A5" s="27"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>43</v>
+      <c r="A6" s="27"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>44</v>
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13" t="s">
+      <c r="A9" s="27"/>
+      <c r="B9" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C9" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D9" s="25" t="s">
         <v>18</v>
       </c>
+      <c r="E9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="7" t="s">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" ht="48" x14ac:dyDescent="0.4">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="7" t="s">
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>49</v>
       </c>
     </row>
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.4">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="16" spans="1:8" ht="48" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="19" spans="1:6" ht="32" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
     <row r="20" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="4" t="s">
+      <c r="A20" s="27"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+    <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D21" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="8" t="s">
+    <row r="22" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>57</v>
       </c>
     </row>
+    <row r="23" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="24" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13" t="s">
+      <c r="A24" s="27"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D24" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="6" t="s">
+    <row r="25" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="26" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A26" s="27"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="27" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>69</v>
+      <c r="A27" s="27"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="6" t="s">
+      <c r="A28" s="27"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14" t="s">
+    <row r="29" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A29" s="27"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>78</v>
       </c>
     </row>
+    <row r="30" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A30" s="27"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
     <row r="31" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>83</v>
+      <c r="A31" s="27"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13" t="s">
+      <c r="A32" s="27"/>
+      <c r="B32" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C32" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D32" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>91</v>
       </c>
     </row>
+    <row r="33" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A33" s="27"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
     <row r="34" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>93</v>
+      <c r="A34" s="27"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>95</v>
+      <c r="A35" s="27"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A36" s="27"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D36" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="80" x14ac:dyDescent="0.4">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="6" t="s">
+    <row r="37" spans="1:6" ht="80" x14ac:dyDescent="0.4">
+      <c r="A37" s="27"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="6" t="s">
+    <row r="38" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A38" s="27"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F38" s="4" t="s">
         <v>104</v>
       </c>
     </row>
+    <row r="39" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A39" s="27"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="40" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="A40" s="27"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D40" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F40" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="4" t="s">
+    <row r="41" spans="1:6" ht="32" x14ac:dyDescent="0.4">
+      <c r="A41" s="27"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="80" x14ac:dyDescent="0.4">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="10" t="s">
+    <row r="42" spans="1:6" ht="80" x14ac:dyDescent="0.4">
+      <c r="A42" s="27"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F42" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13" t="s">
+    <row r="43" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A43" s="27"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D43" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E43" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F43" s="8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="6" t="s">
+    <row r="44" spans="1:6" ht="32" x14ac:dyDescent="0.4">
+      <c r="A44" s="27"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F44" s="8" t="s">
         <v>119</v>
       </c>
     </row>
+    <row r="45" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A45" s="27"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
     <row r="46" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>121</v>
+      <c r="A46" s="27"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>123</v>
+      <c r="A47" s="27"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>126</v>
+      <c r="A48" s="27"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="6" t="s">
+      <c r="A49" s="27"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F49" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13" t="s">
+    <row r="50" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A50" s="27"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F50" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A52" s="12"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="6" t="s">
+    <row r="51" spans="1:6" ht="48" x14ac:dyDescent="0.4">
+      <c r="A51" s="27"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F51" s="8" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A53" s="12"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="6" t="s">
+    <row r="52" spans="1:6" ht="64" x14ac:dyDescent="0.4">
+      <c r="A52" s="27"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F52" s="8" t="s">
         <v>137</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A3:A53"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B10:B32"/>
-    <mergeCell ref="B33:B53"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="C10:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="C44:C53"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D37:D40"/>
-    <mergeCell ref="D41:D43"/>
+  <mergeCells count="29">
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="A2:A52"/>
+    <mergeCell ref="B2:B8"/>
+    <mergeCell ref="B9:B31"/>
+    <mergeCell ref="B32:B52"/>
+    <mergeCell ref="C2:C8"/>
+    <mergeCell ref="C9:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C43:C52"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="D40:D42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2871,7 +4901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D659E6C6-EFCC-4AFC-8D3E-2B5A6272581D}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
@@ -2880,644 +4910,786 @@
     <col min="4" max="4" width="65.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="117.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="1"/>
+    <col min="7" max="7" width="117.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="161.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="48" x14ac:dyDescent="0.4">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="6" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" ht="256" x14ac:dyDescent="0.4">
+      <c r="A3" s="27"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="6" t="s">
+      <c r="G3" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="368" x14ac:dyDescent="0.4">
+      <c r="A4" s="27"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="6" t="s">
+      <c r="G4" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="320" x14ac:dyDescent="0.4">
+      <c r="A5" s="27"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="6" t="s">
+      <c r="G5" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="113.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="27"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.4">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="6" t="s">
+      <c r="G7" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="160" x14ac:dyDescent="0.4">
+      <c r="A8" s="27"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="32" x14ac:dyDescent="0.4">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="6" t="s">
+      <c r="G8" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="144" x14ac:dyDescent="0.4">
+      <c r="A9" s="27"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.4">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="6" t="s">
+      <c r="G9" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="128" x14ac:dyDescent="0.4">
+      <c r="A10" s="27"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="6" t="s">
+      <c r="G10" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="6" t="s">
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.4">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="6" t="s">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="64" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.4">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13" t="s">
+      <c r="G13" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="48" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="64" x14ac:dyDescent="0.4">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="6" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="64" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="6" t="s">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="6" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="6" t="s">
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A18" s="27"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="6" t="s">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="48" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="64" x14ac:dyDescent="0.4">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13" t="s">
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" ht="64" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="6" t="s">
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="48" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="6" t="s">
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13" t="s">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" ht="48" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="6" t="s">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="6" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="6" t="s">
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="27"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="6" t="s">
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="27"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="6" t="s">
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="27"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="6" t="s">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="27"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="6" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A30" s="27"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13" t="s">
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="27"/>
+      <c r="B31" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="6" t="s">
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A32" s="27"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="8" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="6" t="s">
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="27"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="8" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="6" t="s">
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="27"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="8" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13" t="s">
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" ht="115.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="27"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="6" t="s">
+      <c r="G35" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A36" s="27"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="8" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="6" t="s">
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A37" s="27"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="8" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="48" x14ac:dyDescent="0.4">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="6" t="s">
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8" ht="48" x14ac:dyDescent="0.4">
+      <c r="A38" s="27"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="8" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="6" t="s">
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A39" s="27"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="8" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="27"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="8" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="6" t="s">
+      <c r="G40" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A41" s="27"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="8" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="6" t="s">
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A42" s="27"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="8" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A43" s="27"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="8" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="6" t="s">
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A44" s="27"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="8" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="6" t="s">
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A45" s="27"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="8" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13" t="s">
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A46" s="27"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="8" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="6" t="s">
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A47" s="27"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="8" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="32" x14ac:dyDescent="0.4">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="6" t="s">
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" ht="32" x14ac:dyDescent="0.4">
+      <c r="A48" s="27"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="8" t="s">
         <v>244</v>
       </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -3549,554 +5721,649 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7343226F-8FB0-4817-A189-23ACB9A20A6A}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" style="25" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.81640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="118.1796875" style="25" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="25"/>
+    <col min="1" max="1" width="15.6328125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.6328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="118.1796875" style="17" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:11" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="16" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="23" t="s">
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="16" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23" t="s">
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+    </row>
+    <row r="4" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="16" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="21"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22" t="s">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="16" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="16" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23" t="s">
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="16" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22" t="s">
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="16" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="16" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="s">
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="16" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="16" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23" t="s">
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="16" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22" t="s">
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="16" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23" t="s">
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="16" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23" t="s">
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="16" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23" t="s">
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="16" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23" t="s">
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="1:9" ht="391.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="21" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
+      <c r="G17" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="19" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="21"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22" t="s">
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="16" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="21"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23" t="s">
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="16" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23" t="s">
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+    </row>
+    <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="16" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23" t="s">
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="16" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23" t="s">
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="16" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22" t="s">
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+    </row>
+    <row r="24" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="16" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23" t="s">
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="1:9" ht="203" x14ac:dyDescent="0.35">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="19" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="23" t="s">
+      <c r="G25" s="18"/>
+      <c r="H25" s="22" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="16" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="23" t="s">
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+    </row>
+    <row r="27" spans="1:9" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="23" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="21"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23" t="s">
+      <c r="G27" s="18"/>
+      <c r="H27" s="18" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="16" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A29" s="21"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23" t="s">
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+    </row>
+    <row r="29" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="16" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="21"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23" t="s">
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+    </row>
+    <row r="30" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="16" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22" t="s">
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="17" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="16" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="21"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="23" t="s">
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+    </row>
+    <row r="32" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="16" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="21"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="23" t="s">
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+    </row>
+    <row r="33" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="16" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="21"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="23" t="s">
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+    </row>
+    <row r="34" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="19" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="21"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="23" t="s">
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+    </row>
+    <row r="35" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="16" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="21"/>
-      <c r="B36" s="22" t="s">
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+    </row>
+    <row r="36" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="16" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="21"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23" t="s">
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+    </row>
+    <row r="37" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="16" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23" t="s">
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+    </row>
+    <row r="38" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="19" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="21"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="23" t="s">
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+    </row>
+    <row r="39" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="16" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A40" s="21"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23" t="s">
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="16" t="s">
         <v>339</v>
       </c>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4136,516 +6403,515 @@
     <col min="6" max="6" width="140.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="24" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="24" t="s">
         <v>341</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="24" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="25" t="s">
         <v>343</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="14" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="19" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="14" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="19" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="14" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24" t="s">
         <v>350</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="14" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="14" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="116" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="14" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="14" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="19" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="14" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="14" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="24" t="s">
         <v>369</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="14" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="14" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="19" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="14" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="14" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="24" t="s">
         <v>379</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="14" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="14" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="19" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="14" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="14" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19" t="s">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="14" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18" t="s">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24" t="s">
         <v>390</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="24" t="s">
         <v>391</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="14" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="14" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="14" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19" t="s">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="14" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="19" t="s">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="14" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24" t="s">
         <v>402</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="24" t="s">
         <v>403</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="14" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19" t="s">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="14" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="14" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19" t="s">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="14" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="19" t="s">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="14" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="19" t="s">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="14" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18" t="s">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="14" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="19" t="s">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="14" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19" t="s">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="14" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="19" t="s">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="14" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="19" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="14" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="19" t="s">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="14" t="s">
         <v>430</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C32:C37"/>
+    <mergeCell ref="D21:D25"/>
+    <mergeCell ref="D26:D31"/>
+    <mergeCell ref="D32:D37"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="D8:D11"/>
     <mergeCell ref="D12:D15"/>
     <mergeCell ref="D16:D20"/>
-    <mergeCell ref="D21:D25"/>
-    <mergeCell ref="D26:D31"/>
-    <mergeCell ref="D32:D37"/>
     <mergeCell ref="A2:A37"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B31"/>
@@ -4656,6 +6922,7 @@
     <mergeCell ref="C16:C20"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="C26:C31"/>
+    <mergeCell ref="C32:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4673,657 +6940,656 @@
     <col min="6" max="6" width="122.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="24" t="s">
         <v>432</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="24" t="s">
         <v>433</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="24" t="s">
         <v>433</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="14" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="14" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="14" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="14" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="14" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="24" t="s">
         <v>445</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="24" t="s">
         <v>445</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="14" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="14" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24" t="s">
         <v>452</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="24" t="s">
         <v>452</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="14" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="14" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="14" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="14" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="19" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="14" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="14" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="19" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="14" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="14" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="19" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="14" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="14" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18" t="s">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="14" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="19" t="s">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="14" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="14" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="14" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18" t="s">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24" t="s">
         <v>482</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="24" t="s">
         <v>482</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="14" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="19" t="s">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="14" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="19" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="14" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19" t="s">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="14" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="14" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19" t="s">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="14" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="19" t="s">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="14" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18" t="s">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24" t="s">
         <v>497</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="24" t="s">
         <v>498</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="24" t="s">
         <v>498</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="14" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="19" t="s">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="14" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="19" t="s">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="14" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19" t="s">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="14" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="19" t="s">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="14" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="19" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="14" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="19" t="s">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="14" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="19" t="s">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="14" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="19" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="14" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="14" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="19" t="s">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" s="14" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="19" t="s">
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="14" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="19" t="s">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="14" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="19" t="s">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="14" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="19" t="s">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="14" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="19" t="s">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="14" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="19" t="s">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="14" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="19" t="s">
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="14" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="19" t="s">
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="13" t="s">
         <v>536</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="14" t="s">
         <v>537</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C40:C49"/>
+    <mergeCell ref="D31:D39"/>
+    <mergeCell ref="D40:D49"/>
     <mergeCell ref="D2:D6"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="D10:D19"/>
     <mergeCell ref="D20:D23"/>
     <mergeCell ref="D24:D30"/>
-    <mergeCell ref="D31:D39"/>
-    <mergeCell ref="D40:D49"/>
     <mergeCell ref="A2:A49"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B30"/>
@@ -5334,6 +7600,7 @@
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="C24:C30"/>
     <mergeCell ref="C31:C39"/>
+    <mergeCell ref="C40:C49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
